--- a/Documentation/MemoryManagerTables.xlsx
+++ b/Documentation/MemoryManagerTables.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="24030"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10714"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/opt/Source/Favro/Malterlib/Memory/Documentation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFF32A0B-60BC-3D4B-8E60-9753FDFCB9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1840" yWindow="0" windowWidth="25360" windowHeight="17320" tabRatio="500"/>
+    <workbookView xWindow="20280" yWindow="1840" windowWidth="36260" windowHeight="25660" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="1" r:id="rId1"/>
@@ -19,8 +25,19 @@
     <sheet name="7" sheetId="6" r:id="rId10"/>
     <sheet name="15" sheetId="10" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="140000" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -29,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="19">
   <si>
     <t>Size</t>
   </si>
@@ -91,7 +108,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -688,6 +705,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1012,14 +1037,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B4:M126"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B4:M142"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="11" max="11" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>2</v>
       </c>
@@ -1054,7 +1079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -1089,7 +1114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>2</v>
       </c>
@@ -1125,7 +1150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>2</v>
       </c>
@@ -1161,7 +1186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>2</v>
       </c>
@@ -1197,7 +1222,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>2</v>
       </c>
@@ -1233,7 +1258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>2</v>
       </c>
@@ -1269,7 +1294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>2</v>
       </c>
@@ -1305,7 +1330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>2</v>
       </c>
@@ -1341,7 +1366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>2</v>
       </c>
@@ -1377,7 +1402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>2</v>
       </c>
@@ -1413,7 +1438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>2</v>
       </c>
@@ -1449,7 +1474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>2</v>
       </c>
@@ -1485,7 +1510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:13">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>2</v>
       </c>
@@ -1521,7 +1546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>2</v>
       </c>
@@ -1557,7 +1582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>2</v>
       </c>
@@ -1593,7 +1618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>2</v>
       </c>
@@ -1629,7 +1654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>2</v>
       </c>
@@ -1665,7 +1690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>2</v>
       </c>
@@ -1701,7 +1726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>2</v>
       </c>
@@ -1737,7 +1762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>2</v>
       </c>
@@ -1773,7 +1798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>2</v>
       </c>
@@ -1809,7 +1834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:13">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>2</v>
       </c>
@@ -1845,7 +1870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>2</v>
       </c>
@@ -1881,7 +1906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>2</v>
       </c>
@@ -1917,7 +1942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>2</v>
       </c>
@@ -1953,7 +1978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>2</v>
       </c>
@@ -1989,7 +2014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>2</v>
       </c>
@@ -2025,7 +2050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>2</v>
       </c>
@@ -2061,7 +2086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:13">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>2</v>
       </c>
@@ -2097,7 +2122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="2:13">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>2</v>
       </c>
@@ -2133,7 +2158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>2</v>
       </c>
@@ -2169,7 +2194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>2</v>
       </c>
@@ -2205,7 +2230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>2</v>
       </c>
@@ -2241,7 +2266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>2</v>
       </c>
@@ -2277,7 +2302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
         <v>2</v>
       </c>
@@ -2313,7 +2338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
         <v>2</v>
       </c>
@@ -2349,7 +2374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
         <v>2</v>
       </c>
@@ -2385,7 +2410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
         <v>2</v>
       </c>
@@ -2421,7 +2446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
         <v>2</v>
       </c>
@@ -2457,7 +2482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
         <v>2</v>
       </c>
@@ -2493,7 +2518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
         <v>2</v>
       </c>
@@ -2529,7 +2554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
         <v>2</v>
       </c>
@@ -2565,7 +2590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
         <v>2</v>
       </c>
@@ -2601,7 +2626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
         <v>2</v>
       </c>
@@ -2637,7 +2662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="2:13">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
         <v>2</v>
       </c>
@@ -2673,7 +2698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
         <v>2</v>
       </c>
@@ -2709,7 +2734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
         <v>2</v>
       </c>
@@ -2745,7 +2770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
         <v>2</v>
       </c>
@@ -2781,7 +2806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="2:13">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
         <v>2</v>
       </c>
@@ -2817,7 +2842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
         <v>2</v>
       </c>
@@ -2853,7 +2878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
         <v>2</v>
       </c>
@@ -2889,7 +2914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
         <v>2</v>
       </c>
@@ -2925,7 +2950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
         <v>2</v>
       </c>
@@ -2961,7 +2986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
         <v>2</v>
       </c>
@@ -2997,7 +3022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="2:13">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
         <v>2</v>
       </c>
@@ -3033,7 +3058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
         <v>2</v>
       </c>
@@ -3069,7 +3094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
         <v>2</v>
       </c>
@@ -3105,7 +3130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
         <v>2</v>
       </c>
@@ -3141,7 +3166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
         <v>2</v>
       </c>
@@ -3177,7 +3202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
         <v>2</v>
       </c>
@@ -3213,7 +3238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
         <v>2</v>
       </c>
@@ -3249,7 +3274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="2:13">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
         <v>2</v>
       </c>
@@ -3285,7 +3310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
         <v>2</v>
       </c>
@@ -3321,7 +3346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
         <v>2</v>
       </c>
@@ -3357,7 +3382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
         <v>2</v>
       </c>
@@ -3393,7 +3418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
         <v>2</v>
       </c>
@@ -3429,7 +3454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
         <v>2</v>
       </c>
@@ -3466,7 +3491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
         <v>2</v>
       </c>
@@ -3503,7 +3528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="2:13">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
         <v>2</v>
       </c>
@@ -3540,7 +3565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="2:13">
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
         <v>2</v>
       </c>
@@ -3577,7 +3602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
         <v>2</v>
       </c>
@@ -3614,7 +3639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
         <v>2</v>
       </c>
@@ -3651,7 +3676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B77" t="s">
         <v>2</v>
       </c>
@@ -3688,7 +3713,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
         <v>2</v>
       </c>
@@ -3725,7 +3750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
         <v>2</v>
       </c>
@@ -3765,7 +3790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
         <v>2</v>
       </c>
@@ -3802,7 +3827,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="2:13">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B81" t="s">
         <v>2</v>
       </c>
@@ -3839,7 +3864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="2:13">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B82" t="s">
         <v>2</v>
       </c>
@@ -3876,7 +3901,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="2:13">
+    <row r="83" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B83" t="s">
         <v>2</v>
       </c>
@@ -3913,7 +3938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="2:13">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B84" t="s">
         <v>2</v>
       </c>
@@ -3950,7 +3975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="2:13">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B85" t="s">
         <v>2</v>
       </c>
@@ -3987,7 +4012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="2:13">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B86" t="s">
         <v>2</v>
       </c>
@@ -4024,7 +4049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="2:13">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B87" t="s">
         <v>2</v>
       </c>
@@ -4064,7 +4089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="2:13">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B88" t="s">
         <v>2</v>
       </c>
@@ -4101,7 +4126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="2:13">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
         <v>2</v>
       </c>
@@ -4138,7 +4163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="2:13">
+    <row r="90" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B90" t="s">
         <v>2</v>
       </c>
@@ -4175,7 +4200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="2:13">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B91" t="s">
         <v>2</v>
       </c>
@@ -4208,14 +4233,14 @@
         <v>2</v>
       </c>
       <c r="L91" s="5">
-        <f t="shared" ref="L89:L94" si="2">((16*1024*1024-4096)-FLOOR((16*1024*1024-4096)/(C91), 1)*C91)/(16*1024*1024)</f>
+        <f t="shared" ref="L91" si="2">((16*1024*1024-4096)-FLOOR((16*1024*1024-4096)/(C91), 1)*C91)/(16*1024*1024)</f>
         <v>7.32421875E-4</v>
       </c>
       <c r="M91" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="2:13">
+    <row r="92" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B92" t="s">
         <v>2</v>
       </c>
@@ -4252,7 +4277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="2:13">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B93" t="s">
         <v>2</v>
       </c>
@@ -4289,7 +4314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="2:13">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B94" t="s">
         <v>2</v>
       </c>
@@ -4326,7 +4351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="2:13">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B95" t="s">
         <v>2</v>
       </c>
@@ -4366,7 +4391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="2:13">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B96" t="s">
         <v>2</v>
       </c>
@@ -4403,7 +4428,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="2:13">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B97" t="s">
         <v>2</v>
       </c>
@@ -4436,14 +4461,14 @@
         <v>2</v>
       </c>
       <c r="L97" s="5">
-        <f t="shared" ref="L97:L102" si="3">((16*1024*1024-4096)-FLOOR((16*1024*1024-4096)/(C97), 1)*C97)/(16*1024*1024)</f>
+        <f t="shared" ref="L97:L101" si="3">((16*1024*1024-4096)-FLOOR((16*1024*1024-4096)/(C97), 1)*C97)/(16*1024*1024)</f>
         <v>1.220703125E-3</v>
       </c>
       <c r="M97" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="2:13">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B98" t="s">
         <v>2</v>
       </c>
@@ -4480,7 +4505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="2:13">
+    <row r="99" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B99" t="s">
         <v>2</v>
       </c>
@@ -4520,7 +4545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="2:13">
+    <row r="100" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
         <v>2</v>
       </c>
@@ -4557,7 +4582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="2:13">
+    <row r="101" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B101" t="s">
         <v>2</v>
       </c>
@@ -4597,7 +4622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="2:13">
+    <row r="102" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B102" t="s">
         <v>2</v>
       </c>
@@ -4634,7 +4659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="2:13">
+    <row r="103" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B103" t="s">
         <v>2</v>
       </c>
@@ -4674,7 +4699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="2:13">
+    <row r="104" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B104" t="s">
         <v>2</v>
       </c>
@@ -4714,7 +4739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="2:13">
+    <row r="105" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B105" t="s">
         <v>2</v>
       </c>
@@ -4754,7 +4779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="2:13">
+    <row r="106" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B106" t="s">
         <v>2</v>
       </c>
@@ -4791,7 +4816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="2:13">
+    <row r="107" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B107" t="s">
         <v>2</v>
       </c>
@@ -4831,7 +4856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="2:13">
+    <row r="108" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B108" t="s">
         <v>2</v>
       </c>
@@ -4871,7 +4896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="2:13">
+    <row r="109" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B109" t="s">
         <v>2</v>
       </c>
@@ -4911,7 +4936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="2:13">
+    <row r="110" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B110" t="s">
         <v>2</v>
       </c>
@@ -4951,7 +4976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="2:13">
+    <row r="111" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
         <v>2</v>
       </c>
@@ -4991,7 +5016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="2:13">
+    <row r="112" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
         <v>2</v>
       </c>
@@ -5031,7 +5056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="2:13">
+    <row r="113" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B113" t="s">
         <v>2</v>
       </c>
@@ -5071,7 +5096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="2:13">
+    <row r="114" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
         <v>2</v>
       </c>
@@ -5108,7 +5133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="2:13">
+    <row r="115" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
         <v>2</v>
       </c>
@@ -5148,7 +5173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="2:13">
+    <row r="116" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
         <v>2</v>
       </c>
@@ -5188,7 +5213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="2:13">
+    <row r="117" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
         <v>2</v>
       </c>
@@ -5228,7 +5253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="2:13">
+    <row r="118" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
         <v>2</v>
       </c>
@@ -5268,7 +5293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="2:13">
+    <row r="119" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
         <v>2</v>
       </c>
@@ -5308,7 +5333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="2:13">
+    <row r="120" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
         <v>2</v>
       </c>
@@ -5348,7 +5373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="2:13">
+    <row r="121" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
         <v>2</v>
       </c>
@@ -5388,7 +5413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="2:13">
+    <row r="122" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
         <v>2</v>
       </c>
@@ -5428,7 +5453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="2:13">
+    <row r="123" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
         <v>2</v>
       </c>
@@ -5468,7 +5493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="2:13">
+    <row r="124" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
         <v>2</v>
       </c>
@@ -5508,7 +5533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="2:13">
+    <row r="125" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
         <v>2</v>
       </c>
@@ -5548,7 +5573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="2:13">
+    <row r="126" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
         <v>2</v>
       </c>
@@ -5585,6 +5610,646 @@
         <v>3.662109375E-3</v>
       </c>
       <c r="M126" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B127" t="s">
+        <v>2</v>
+      </c>
+      <c r="C127">
+        <v>524288</v>
+      </c>
+      <c r="D127" t="s">
+        <v>2</v>
+      </c>
+      <c r="E127" t="s">
+        <v>17</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127" t="s">
+        <v>2</v>
+      </c>
+      <c r="H127">
+        <v>4096</v>
+      </c>
+      <c r="I127" t="s">
+        <v>2</v>
+      </c>
+      <c r="J127">
+        <f t="shared" ref="J127:J142" si="7">IF(C127/H127&gt;=1,C127/H127,"")</f>
+        <v>128</v>
+      </c>
+      <c r="K127" t="s">
+        <v>2</v>
+      </c>
+      <c r="L127" s="5">
+        <f>((16*1024*1024-4096*3)-FLOOR((16*1024*1024-4096*3)/(C127), 1)*C127)/(16*1024*1024)</f>
+        <v>3.0517578125E-2</v>
+      </c>
+      <c r="M127" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B128" t="s">
+        <v>2</v>
+      </c>
+      <c r="C128">
+        <v>589824</v>
+      </c>
+      <c r="D128" t="s">
+        <v>2</v>
+      </c>
+      <c r="E128" t="s">
+        <v>17</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128" t="s">
+        <v>2</v>
+      </c>
+      <c r="H128">
+        <v>36864</v>
+      </c>
+      <c r="I128" t="s">
+        <v>2</v>
+      </c>
+      <c r="J128">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="K128" t="s">
+        <v>2</v>
+      </c>
+      <c r="L128" s="5">
+        <f>((16*1024*1024-4096)-FLOOR((16*1024*1024-4096)/(C128), 1)*C128)/(16*1024*1024)</f>
+        <v>1.5380859375E-2</v>
+      </c>
+      <c r="M128" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B129" t="s">
+        <v>2</v>
+      </c>
+      <c r="C129">
+        <v>655360</v>
+      </c>
+      <c r="D129" t="s">
+        <v>2</v>
+      </c>
+      <c r="E129" t="s">
+        <v>17</v>
+      </c>
+      <c r="F129">
+        <v>2</v>
+      </c>
+      <c r="G129" t="s">
+        <v>2</v>
+      </c>
+      <c r="H129">
+        <v>20480</v>
+      </c>
+      <c r="I129" t="s">
+        <v>2</v>
+      </c>
+      <c r="J129">
+        <f t="shared" si="7"/>
+        <v>32</v>
+      </c>
+      <c r="K129" t="s">
+        <v>2</v>
+      </c>
+      <c r="L129" s="5">
+        <f t="shared" ref="L129:L134" si="8">((16*1024*1024-4096)-FLOOR((16*1024*1024-4096)/(C129), 1)*C129)/(16*1024*1024)</f>
+        <v>2.3193359375E-2</v>
+      </c>
+      <c r="M129" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B130" t="s">
+        <v>2</v>
+      </c>
+      <c r="C130">
+        <v>720896</v>
+      </c>
+      <c r="D130" t="s">
+        <v>2</v>
+      </c>
+      <c r="E130" t="s">
+        <v>17</v>
+      </c>
+      <c r="F130">
+        <v>3</v>
+      </c>
+      <c r="G130" t="s">
+        <v>2</v>
+      </c>
+      <c r="H130">
+        <v>45056</v>
+      </c>
+      <c r="I130" t="s">
+        <v>2</v>
+      </c>
+      <c r="J130">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="K130" t="s">
+        <v>2</v>
+      </c>
+      <c r="L130" s="5">
+        <f>((16*1024*1024-4096*4)-FLOOR((16*1024*1024-4096*4)/(C130), 1)*C130)/(16*1024*1024)</f>
+        <v>1.07421875E-2</v>
+      </c>
+      <c r="M130" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B131" t="s">
+        <v>2</v>
+      </c>
+      <c r="C131">
+        <v>786432</v>
+      </c>
+      <c r="D131" t="s">
+        <v>2</v>
+      </c>
+      <c r="E131" t="s">
+        <v>17</v>
+      </c>
+      <c r="F131">
+        <v>4</v>
+      </c>
+      <c r="G131" t="s">
+        <v>2</v>
+      </c>
+      <c r="H131">
+        <v>12288</v>
+      </c>
+      <c r="I131" t="s">
+        <v>2</v>
+      </c>
+      <c r="J131">
+        <f t="shared" si="7"/>
+        <v>64</v>
+      </c>
+      <c r="K131" t="s">
+        <v>2</v>
+      </c>
+      <c r="L131" s="5">
+        <f t="shared" ref="L131:L134" si="9">((16*1024*1024-4096)-FLOOR((16*1024*1024-4096)/(C131), 1)*C131)/(16*1024*1024)</f>
+        <v>1.5380859375E-2</v>
+      </c>
+      <c r="M131" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B132" t="s">
+        <v>2</v>
+      </c>
+      <c r="C132">
+        <v>851968</v>
+      </c>
+      <c r="D132" t="s">
+        <v>2</v>
+      </c>
+      <c r="E132" t="s">
+        <v>17</v>
+      </c>
+      <c r="F132">
+        <v>5</v>
+      </c>
+      <c r="G132" t="s">
+        <v>2</v>
+      </c>
+      <c r="H132">
+        <v>53248</v>
+      </c>
+      <c r="I132" t="s">
+        <v>2</v>
+      </c>
+      <c r="J132">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="K132" t="s">
+        <v>2</v>
+      </c>
+      <c r="L132" s="5">
+        <f t="shared" si="9"/>
+        <v>3.4912109375E-2</v>
+      </c>
+      <c r="M132" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B133" t="s">
+        <v>2</v>
+      </c>
+      <c r="C133">
+        <v>917504</v>
+      </c>
+      <c r="D133" t="s">
+        <v>2</v>
+      </c>
+      <c r="E133" t="s">
+        <v>17</v>
+      </c>
+      <c r="F133">
+        <v>6</v>
+      </c>
+      <c r="G133" t="s">
+        <v>2</v>
+      </c>
+      <c r="H133">
+        <v>28672</v>
+      </c>
+      <c r="I133" t="s">
+        <v>2</v>
+      </c>
+      <c r="J133">
+        <f t="shared" si="7"/>
+        <v>32</v>
+      </c>
+      <c r="K133" t="s">
+        <v>2</v>
+      </c>
+      <c r="L133" s="5">
+        <f t="shared" si="9"/>
+        <v>1.5380859375E-2</v>
+      </c>
+      <c r="M133" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B134" t="s">
+        <v>2</v>
+      </c>
+      <c r="C134">
+        <v>983040</v>
+      </c>
+      <c r="D134" t="s">
+        <v>2</v>
+      </c>
+      <c r="E134" t="s">
+        <v>17</v>
+      </c>
+      <c r="F134">
+        <v>7</v>
+      </c>
+      <c r="G134" t="s">
+        <v>2</v>
+      </c>
+      <c r="H134">
+        <v>61440</v>
+      </c>
+      <c r="I134" t="s">
+        <v>2</v>
+      </c>
+      <c r="J134">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="K134" t="s">
+        <v>2</v>
+      </c>
+      <c r="L134" s="5">
+        <f t="shared" si="9"/>
+        <v>3.662109375E-3</v>
+      </c>
+      <c r="M134" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B135" t="s">
+        <v>2</v>
+      </c>
+      <c r="C135">
+        <v>1048576</v>
+      </c>
+      <c r="D135" t="s">
+        <v>2</v>
+      </c>
+      <c r="E135" t="s">
+        <v>17</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135" t="s">
+        <v>2</v>
+      </c>
+      <c r="H135">
+        <v>4096</v>
+      </c>
+      <c r="I135" t="s">
+        <v>2</v>
+      </c>
+      <c r="J135">
+        <f t="shared" si="7"/>
+        <v>256</v>
+      </c>
+      <c r="K135" t="s">
+        <v>2</v>
+      </c>
+      <c r="L135" s="5">
+        <f>((16*1024*1024-4096*3)-FLOOR((16*1024*1024-4096*3)/(C135), 1)*C135)/(16*1024*1024)</f>
+        <v>6.1767578125E-2</v>
+      </c>
+      <c r="M135" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B136" t="s">
+        <v>2</v>
+      </c>
+      <c r="C136">
+        <v>1179648</v>
+      </c>
+      <c r="D136" t="s">
+        <v>2</v>
+      </c>
+      <c r="E136" t="s">
+        <v>17</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136" t="s">
+        <v>2</v>
+      </c>
+      <c r="H136">
+        <v>36864</v>
+      </c>
+      <c r="I136" t="s">
+        <v>2</v>
+      </c>
+      <c r="J136">
+        <f t="shared" si="7"/>
+        <v>32</v>
+      </c>
+      <c r="K136" t="s">
+        <v>2</v>
+      </c>
+      <c r="L136" s="5">
+        <f>((16*1024*1024-4096)-FLOOR((16*1024*1024-4096)/(C136), 1)*C136)/(16*1024*1024)</f>
+        <v>1.5380859375E-2</v>
+      </c>
+      <c r="M136" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B137" t="s">
+        <v>2</v>
+      </c>
+      <c r="C137">
+        <v>1310720</v>
+      </c>
+      <c r="D137" t="s">
+        <v>2</v>
+      </c>
+      <c r="E137" t="s">
+        <v>17</v>
+      </c>
+      <c r="F137">
+        <v>2</v>
+      </c>
+      <c r="G137" t="s">
+        <v>2</v>
+      </c>
+      <c r="H137">
+        <v>20480</v>
+      </c>
+      <c r="I137" t="s">
+        <v>2</v>
+      </c>
+      <c r="J137">
+        <f t="shared" si="7"/>
+        <v>64</v>
+      </c>
+      <c r="K137" t="s">
+        <v>2</v>
+      </c>
+      <c r="L137" s="5">
+        <f t="shared" ref="L137:L142" si="10">((16*1024*1024-4096)-FLOOR((16*1024*1024-4096)/(C137), 1)*C137)/(16*1024*1024)</f>
+        <v>6.2255859375E-2</v>
+      </c>
+      <c r="M137" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C138">
+        <v>1441792</v>
+      </c>
+      <c r="D138" t="s">
+        <v>2</v>
+      </c>
+      <c r="E138" t="s">
+        <v>17</v>
+      </c>
+      <c r="F138">
+        <v>3</v>
+      </c>
+      <c r="G138" t="s">
+        <v>2</v>
+      </c>
+      <c r="H138">
+        <v>45056</v>
+      </c>
+      <c r="I138" t="s">
+        <v>2</v>
+      </c>
+      <c r="J138">
+        <f t="shared" si="7"/>
+        <v>32</v>
+      </c>
+      <c r="K138" t="s">
+        <v>2</v>
+      </c>
+      <c r="L138" s="5">
+        <f>((16*1024*1024-4096*4)-FLOOR((16*1024*1024-4096*4)/(C138), 1)*C138)/(16*1024*1024)</f>
+        <v>5.37109375E-2</v>
+      </c>
+      <c r="M138" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B139" t="s">
+        <v>2</v>
+      </c>
+      <c r="C139">
+        <v>1572864</v>
+      </c>
+      <c r="D139" t="s">
+        <v>2</v>
+      </c>
+      <c r="E139" t="s">
+        <v>17</v>
+      </c>
+      <c r="F139">
+        <v>4</v>
+      </c>
+      <c r="G139" t="s">
+        <v>2</v>
+      </c>
+      <c r="H139">
+        <v>12288</v>
+      </c>
+      <c r="I139" t="s">
+        <v>2</v>
+      </c>
+      <c r="J139">
+        <f t="shared" si="7"/>
+        <v>128</v>
+      </c>
+      <c r="K139" t="s">
+        <v>2</v>
+      </c>
+      <c r="L139" s="5">
+        <f t="shared" ref="L139:L142" si="11">((16*1024*1024-4096)-FLOOR((16*1024*1024-4096)/(C139), 1)*C139)/(16*1024*1024)</f>
+        <v>6.2255859375E-2</v>
+      </c>
+      <c r="M139" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B140" t="s">
+        <v>2</v>
+      </c>
+      <c r="C140">
+        <v>1703936</v>
+      </c>
+      <c r="D140" t="s">
+        <v>2</v>
+      </c>
+      <c r="E140" t="s">
+        <v>17</v>
+      </c>
+      <c r="F140">
+        <v>5</v>
+      </c>
+      <c r="G140" t="s">
+        <v>2</v>
+      </c>
+      <c r="H140">
+        <v>53248</v>
+      </c>
+      <c r="I140" t="s">
+        <v>2</v>
+      </c>
+      <c r="J140">
+        <f t="shared" si="7"/>
+        <v>32</v>
+      </c>
+      <c r="K140" t="s">
+        <v>2</v>
+      </c>
+      <c r="L140" s="5">
+        <f t="shared" si="11"/>
+        <v>8.5693359375E-2</v>
+      </c>
+      <c r="M140" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C141">
+        <v>1835008</v>
+      </c>
+      <c r="D141" t="s">
+        <v>2</v>
+      </c>
+      <c r="E141" t="s">
+        <v>17</v>
+      </c>
+      <c r="F141">
+        <v>6</v>
+      </c>
+      <c r="G141" t="s">
+        <v>2</v>
+      </c>
+      <c r="H141">
+        <v>28672</v>
+      </c>
+      <c r="I141" t="s">
+        <v>2</v>
+      </c>
+      <c r="J141">
+        <f t="shared" si="7"/>
+        <v>64</v>
+      </c>
+      <c r="K141" t="s">
+        <v>2</v>
+      </c>
+      <c r="L141" s="5">
+        <f t="shared" si="11"/>
+        <v>1.5380859375E-2</v>
+      </c>
+      <c r="M141" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B142" t="s">
+        <v>2</v>
+      </c>
+      <c r="C142">
+        <v>1966080</v>
+      </c>
+      <c r="D142" t="s">
+        <v>2</v>
+      </c>
+      <c r="E142" t="s">
+        <v>17</v>
+      </c>
+      <c r="F142">
+        <v>7</v>
+      </c>
+      <c r="G142" t="s">
+        <v>2</v>
+      </c>
+      <c r="H142">
+        <v>61440</v>
+      </c>
+      <c r="I142" t="s">
+        <v>2</v>
+      </c>
+      <c r="J142">
+        <f t="shared" si="7"/>
+        <v>32</v>
+      </c>
+      <c r="K142" t="s">
+        <v>2</v>
+      </c>
+      <c r="L142" s="5">
+        <f t="shared" si="11"/>
+        <v>6.2255859375E-2</v>
+      </c>
+      <c r="M142" t="s">
         <v>2</v>
       </c>
     </row>
@@ -5600,11 +6265,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B5:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
@@ -5633,7 +6298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
@@ -5662,7 +6327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
@@ -5686,7 +6351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
@@ -5710,7 +6375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>2</v>
       </c>
@@ -5734,7 +6399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>2</v>
       </c>
@@ -5758,7 +6423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
@@ -5782,7 +6447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
@@ -5806,7 +6471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
@@ -5830,7 +6495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
@@ -5854,7 +6519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
@@ -5879,7 +6544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>2</v>
       </c>
@@ -5904,7 +6569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>2</v>
       </c>
@@ -5931,7 +6596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
@@ -5954,14 +6619,14 @@
         <v>2</v>
       </c>
       <c r="I18" s="5">
-        <f t="shared" ref="I15:I20" si="0">(16*1024*1024-FLOOR((16*1024*1024-4096)/(C18), 1)*C18-4096)/(16*1024*1024)</f>
+        <f t="shared" ref="I18:I19" si="0">(16*1024*1024-FLOOR((16*1024*1024-4096)/(C18), 1)*C18-4096)/(16*1024*1024)</f>
         <v>1.708984375E-3</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>2</v>
       </c>
@@ -5991,7 +6656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
@@ -6021,7 +6686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>2</v>
       </c>
@@ -6051,7 +6716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>2</v>
       </c>
@@ -6064,7 +6729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>2</v>
       </c>
@@ -6081,7 +6746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
@@ -6098,7 +6763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>2</v>
       </c>
@@ -6116,7 +6781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>2</v>
       </c>
@@ -6133,7 +6798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>2</v>
       </c>
@@ -6150,7 +6815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>2</v>
       </c>
@@ -6167,7 +6832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>2</v>
       </c>
@@ -6200,11 +6865,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B3:J30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
@@ -6233,7 +6898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
@@ -6262,7 +6927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
@@ -6286,7 +6951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
@@ -6310,7 +6975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
@@ -6334,7 +6999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
@@ -6358,7 +7023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>2</v>
       </c>
@@ -6382,7 +7047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>2</v>
       </c>
@@ -6406,7 +7071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
@@ -6430,7 +7095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
@@ -6454,7 +7119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
@@ -6479,7 +7144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
@@ -6504,7 +7169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
@@ -6531,7 +7196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>2</v>
       </c>
@@ -6554,14 +7219,14 @@
         <v>2</v>
       </c>
       <c r="I16" s="5">
-        <f t="shared" ref="I16:I19" si="0">(16*1024*1024-FLOOR((16*1024*1024-4096)/(C16), 1)*C16-4096)/(16*1024*1024)</f>
+        <f t="shared" ref="I16:I17" si="0">(16*1024*1024-FLOOR((16*1024*1024-4096)/(C16), 1)*C16-4096)/(16*1024*1024)</f>
         <v>3.662109375E-3</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>2</v>
       </c>
@@ -6591,7 +7256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
@@ -6621,11 +7286,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="I19" s="5"/>
       <c r="J19" s="2"/>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>2</v>
       </c>
@@ -6638,7 +7303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>2</v>
       </c>
@@ -6655,7 +7320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>2</v>
       </c>
@@ -6672,7 +7337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>2</v>
       </c>
@@ -6690,7 +7355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>2</v>
       </c>
@@ -6707,7 +7372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
@@ -6724,7 +7389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>2</v>
       </c>
@@ -6741,7 +7406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>2</v>
       </c>
@@ -6774,11 +7439,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B5:K22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="5" spans="2:11">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -6807,7 +7472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:11">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>2</v>
       </c>
@@ -6839,7 +7504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:11">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>2</v>
       </c>
@@ -6872,7 +7537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:11">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>2</v>
       </c>
@@ -6905,7 +7570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:11">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>2</v>
       </c>
@@ -6938,7 +7603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:11">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>2</v>
       </c>
@@ -6971,7 +7636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:11">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>2</v>
       </c>
@@ -7004,7 +7669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:11">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>2</v>
       </c>
@@ -7037,7 +7702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:11">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>2</v>
       </c>
@@ -7070,7 +7735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:11">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>2</v>
       </c>
@@ -7103,7 +7768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:11">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>2</v>
       </c>
@@ -7136,7 +7801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:11">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>2</v>
       </c>
@@ -7169,7 +7834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:11">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>2</v>
       </c>
@@ -7202,7 +7867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:11">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>2</v>
       </c>
@@ -7235,7 +7900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:11">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>2</v>
       </c>
@@ -7268,7 +7933,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:11">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>2</v>
       </c>
@@ -7301,7 +7966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:11">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>2</v>
       </c>
@@ -7334,7 +7999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="2:11">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>2</v>
       </c>
@@ -7379,11 +8044,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B5:K12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="5" spans="2:11">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -7412,7 +8077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:11">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>2</v>
       </c>
@@ -7442,7 +8107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:11">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>2</v>
       </c>
@@ -7475,7 +8140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:11">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>2</v>
       </c>
@@ -7508,7 +8173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:11">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>2</v>
       </c>
@@ -7541,7 +8206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:11">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>2</v>
       </c>
@@ -7574,7 +8239,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:11">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>2</v>
       </c>
@@ -7607,7 +8272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:11">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>2</v>
       </c>
@@ -7652,15 +8317,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B5:K41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
@@ -7689,7 +8354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
@@ -7718,7 +8383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
@@ -7742,7 +8407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
@@ -7766,7 +8431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>2</v>
       </c>
@@ -7790,7 +8455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>2</v>
       </c>
@@ -7814,7 +8479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
@@ -7838,7 +8503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
@@ -7862,7 +8527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
@@ -7886,7 +8551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
@@ -7912,7 +8577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
@@ -7942,7 +8607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>2</v>
       </c>
@@ -7972,7 +8637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>2</v>
       </c>
@@ -8002,7 +8667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
@@ -8032,7 +8697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>2</v>
       </c>
@@ -8062,7 +8727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
@@ -8092,7 +8757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>2</v>
       </c>
@@ -8107,7 +8772,7 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>2</v>
       </c>
@@ -8126,7 +8791,7 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>2</v>
       </c>
@@ -8145,7 +8810,7 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>2</v>
       </c>
@@ -8165,7 +8830,7 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>2</v>
       </c>
@@ -8184,7 +8849,7 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
@@ -8204,7 +8869,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>2</v>
       </c>
@@ -8223,7 +8888,7 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>2</v>
       </c>
@@ -8243,7 +8908,7 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -8252,7 +8917,7 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -8261,7 +8926,7 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="2:11">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -8270,7 +8935,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="2:11">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>2</v>
       </c>
@@ -8299,7 +8964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="2:11">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>2</v>
       </c>
@@ -8329,7 +8994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="2:11">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>2</v>
       </c>
@@ -8362,7 +9027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:11">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>2</v>
       </c>
@@ -8395,7 +9060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:11">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>2</v>
       </c>
@@ -8428,7 +9093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:11">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
         <v>2</v>
       </c>
@@ -8461,7 +9126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:11">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
         <v>2</v>
       </c>
@@ -8494,7 +9159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="2:11">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
         <v>2</v>
       </c>
@@ -8539,11 +9204,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B5:J32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
@@ -8572,7 +9237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
@@ -8601,7 +9266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
@@ -8625,7 +9290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
@@ -8649,7 +9314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>2</v>
       </c>
@@ -8673,7 +9338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>2</v>
       </c>
@@ -8697,7 +9362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
@@ -8721,7 +9386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
@@ -8745,7 +9410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
@@ -8769,7 +9434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
@@ -8793,7 +9458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
@@ -8818,7 +9483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>2</v>
       </c>
@@ -8843,7 +9508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>2</v>
       </c>
@@ -8870,7 +9535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
@@ -8893,14 +9558,14 @@
         <v>2</v>
       </c>
       <c r="I18" s="5">
-        <f t="shared" ref="I15:I20" si="0">(16*1024*1024-FLOOR((16*1024*1024-4096)/(C18), 1)*C18-4096)/(16*1024*1024)</f>
+        <f t="shared" ref="I18:I19" si="0">(16*1024*1024-FLOOR((16*1024*1024-4096)/(C18), 1)*C18-4096)/(16*1024*1024)</f>
         <v>2.197265625E-3</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>2</v>
       </c>
@@ -8930,7 +9595,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
@@ -8960,7 +9625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>2</v>
       </c>
@@ -8973,7 +9638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>2</v>
       </c>
@@ -8990,7 +9655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>2</v>
       </c>
@@ -9007,7 +9672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
@@ -9025,7 +9690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>2</v>
       </c>
@@ -9042,7 +9707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>2</v>
       </c>
@@ -9059,7 +9724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>2</v>
       </c>
@@ -9076,7 +9741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>2</v>
       </c>
@@ -9109,11 +9774,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B4:J32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
@@ -9142,7 +9807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
@@ -9171,7 +9836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
@@ -9195,7 +9860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
@@ -9219,7 +9884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
@@ -9243,7 +9908,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>2</v>
       </c>
@@ -9267,7 +9932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>2</v>
       </c>
@@ -9291,7 +9956,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
@@ -9315,7 +9980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
@@ -9339,7 +10004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
@@ -9363,7 +10028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
@@ -9388,7 +10053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
@@ -9413,7 +10078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>2</v>
       </c>
@@ -9440,7 +10105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>2</v>
       </c>
@@ -9463,14 +10128,14 @@
         <v>2</v>
       </c>
       <c r="I17" s="5">
-        <f t="shared" ref="I14:I19" si="0">(16*1024*1024-FLOOR((16*1024*1024-4096)/(C17), 1)*C17-4096)/(16*1024*1024)</f>
+        <f t="shared" ref="I17:I18" si="0">(16*1024*1024-FLOOR((16*1024*1024-4096)/(C17), 1)*C17-4096)/(16*1024*1024)</f>
         <v>1.220703125E-3</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
@@ -9500,7 +10165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>2</v>
       </c>
@@ -9530,7 +10195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
@@ -9560,7 +10225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>2</v>
       </c>
@@ -9573,7 +10238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>2</v>
       </c>
@@ -9590,7 +10255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>2</v>
       </c>
@@ -9607,7 +10272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
@@ -9625,7 +10290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>2</v>
       </c>
@@ -9642,7 +10307,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>2</v>
       </c>
@@ -9659,7 +10324,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>2</v>
       </c>
@@ -9676,7 +10341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>2</v>
       </c>
@@ -9709,14 +10374,14 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B5:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="21.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
@@ -9745,7 +10410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
@@ -9774,7 +10439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
@@ -9798,7 +10463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
@@ -9822,7 +10487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>2</v>
       </c>
@@ -9846,7 +10511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>2</v>
       </c>
@@ -9870,7 +10535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
@@ -9894,7 +10559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
@@ -9918,7 +10583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
@@ -9942,7 +10607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
@@ -9966,7 +10631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
@@ -9991,7 +10656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>2</v>
       </c>
@@ -10016,7 +10681,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>2</v>
       </c>
@@ -10043,7 +10708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
@@ -10070,7 +10735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>2</v>
       </c>
@@ -10097,7 +10762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
@@ -10120,14 +10785,14 @@
         <v>2</v>
       </c>
       <c r="I20" s="5">
-        <f t="shared" ref="I16:I20" si="0">((16*1024*1024-4096*4)-FLOOR((16*1024*1024-4096*4)/(C20), 1)*C20)/(16*1024*1024)</f>
+        <f t="shared" ref="I20" si="0">((16*1024*1024-4096*4)-FLOOR((16*1024*1024-4096*4)/(C20), 1)*C20)/(16*1024*1024)</f>
         <v>1.07421875E-2</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>2</v>
       </c>
@@ -10140,7 +10805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>2</v>
       </c>
@@ -10157,7 +10822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
@@ -10174,7 +10839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>2</v>
       </c>
@@ -10192,7 +10857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>2</v>
       </c>
@@ -10209,7 +10874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>2</v>
       </c>
@@ -10226,7 +10891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>2</v>
       </c>
@@ -10244,7 +10909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>2</v>
       </c>
@@ -10274,11 +10939,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A5:J32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
@@ -10307,7 +10972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
@@ -10336,7 +11001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
@@ -10360,7 +11025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
@@ -10384,7 +11049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>2</v>
       </c>
@@ -10408,7 +11073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>2</v>
       </c>
@@ -10432,7 +11097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
@@ -10456,7 +11121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
@@ -10480,7 +11145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
@@ -10504,7 +11169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
@@ -10528,7 +11193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
@@ -10553,7 +11218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>2</v>
       </c>
@@ -10580,7 +11245,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>2</v>
       </c>
@@ -10603,14 +11268,14 @@
         <v>2</v>
       </c>
       <c r="I17" s="5">
-        <f t="shared" ref="I15:I20" si="0">(16*1024*1024-FLOOR((16*1024*1024-4096)/(C17), 1)*C17-4096)/(16*1024*1024)</f>
+        <f t="shared" ref="I17:I19" si="0">(16*1024*1024-FLOOR((16*1024*1024-4096)/(C17), 1)*C17-4096)/(16*1024*1024)</f>
         <v>7.32421875E-4</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
@@ -10640,7 +11305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>2</v>
       </c>
@@ -10670,7 +11335,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
@@ -10700,7 +11365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>2</v>
       </c>
@@ -10730,7 +11395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>2</v>
       </c>
@@ -10743,7 +11408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>2</v>
       </c>
@@ -10760,7 +11425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
         <v>2</v>
@@ -10780,7 +11445,7 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
         <v>2</v>
@@ -10801,7 +11466,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>2</v>
       </c>
@@ -10818,7 +11483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>2</v>
       </c>
@@ -10835,7 +11500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>2</v>
       </c>
@@ -10852,7 +11517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>2</v>
       </c>
@@ -10885,14 +11550,14 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B5:J32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="20.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
@@ -10921,7 +11586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
@@ -10950,7 +11615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
@@ -10974,7 +11639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
@@ -10998,7 +11663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>2</v>
       </c>
@@ -11022,7 +11687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>2</v>
       </c>
@@ -11046,7 +11711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
@@ -11070,7 +11735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
@@ -11094,7 +11759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
@@ -11118,7 +11783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
@@ -11142,7 +11807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
@@ -11167,7 +11832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>2</v>
       </c>
@@ -11192,7 +11857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>2</v>
       </c>
@@ -11219,7 +11884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
@@ -11242,14 +11907,14 @@
         <v>2</v>
       </c>
       <c r="I18" s="5">
-        <f t="shared" ref="I15:I20" si="0">(16*1024*1024-FLOOR((16*1024*1024-4096)/(C18), 1)*C18-4096)/(16*1024*1024)</f>
+        <f t="shared" ref="I18:I19" si="0">(16*1024*1024-FLOOR((16*1024*1024-4096)/(C18), 1)*C18-4096)/(16*1024*1024)</f>
         <v>3.173828125E-3</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>2</v>
       </c>
@@ -11279,7 +11944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
@@ -11309,7 +11974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>2</v>
       </c>
@@ -11322,7 +11987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>2</v>
       </c>
@@ -11339,7 +12004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>2</v>
       </c>
@@ -11356,7 +12021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
@@ -11374,7 +12039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>2</v>
       </c>
@@ -11391,7 +12056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>2</v>
       </c>
@@ -11408,7 +12073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>2</v>
       </c>
@@ -11425,7 +12090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>2</v>
       </c>
